--- a/evaluation_result.xlsx
+++ b/evaluation_result.xlsx
@@ -458,7 +458,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
@@ -468,7 +468,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.48</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="5">
@@ -755,7 +755,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
@@ -2583,7 +2583,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>

--- a/evaluation_result.xlsx
+++ b/evaluation_result.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,41 +454,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>成功返回结果数</t>
+          <t>已标注预期ID题目数</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>命中率</t>
+          <t>成功返回结果数</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>精确命中数</t>
+          <t>命中率</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>精确命中数</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Top1精确命中率</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>0</v>
+      <c r="B7" t="n">
+        <v>0.925</v>
       </c>
     </row>
   </sheetData>
@@ -588,22 +598,22 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>大连海洋大学心理咨询怎么网站预约？</t>
+          <t>新生线上报到一般通过什么系统完成？</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>报到与迎新</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>网站预约</t>
+          <t>线上报到</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -613,7 +623,7 @@
       </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>2.81</v>
+        <v>4.99</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -634,35 +644,43 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>大连海洋大学校园网账号是什么？</t>
+          <t>新生线上报到一般通过什么系统完成？</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>报到与迎新</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>账号</t>
+          <t>线上报到</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>3.33</v>
+        <v>23.2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -683,35 +701,43 @@
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>校园网有问题去哪里看或找谁？</t>
+          <t>新生入学前学校会提前推送哪些信息？</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>报到与迎新</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>入学信息推送</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>2.72</v>
+        <v>20.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -735,32 +761,32 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>校园卡绑定后可以做什么？</t>
+          <t>新生线上报到一般通过什么系统完成？</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>校园卡</t>
+          <t>报到与迎新</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>使用</t>
+          <t>线上报到</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>4.6</v>
+        <v>5.38</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -781,35 +807,43 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>校园网有问题去哪里看或找谁？</t>
+          <t>学校迎新主要涉及哪些校区？</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>报到与迎新</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>校区</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>3.19</v>
+        <v>24.55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -879,39 +913,47 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>校园网账号开通和使用规则是什么？</t>
+          <t>家庭经济困难新生如何申请绿色通道？</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>资助与帮扶</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>规则</t>
+          <t>绿色通道</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>1.06</v>
+        <v>24.63</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -928,39 +970,47 @@
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>校园卡丢了怎么办？</t>
+          <t>绿色通道一般在什么时候、什么场景下办理？</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>校园卡</t>
+          <t>资助与帮扶</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>挂失/解挂</t>
+          <t>绿色通道</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>2.99</v>
+        <v>25.52</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -980,32 +1030,32 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>校园网有问题去哪里看或找谁？</t>
+          <t>学校迎新主要涉及哪些校区？</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>报到与迎新</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>校区</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="n">
-        <v>1.77</v>
+        <v>7.82</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1029,12 +1079,12 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>大黑石校区心理预约电话是多少？</t>
+          <t>不同校区的心理咨询服务怎么区分？</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1044,7 +1094,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>电话预约</t>
+          <t>校区服务</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1054,7 +1104,7 @@
       </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>5.52</v>
+        <v>6.64</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -1078,32 +1128,32 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>大连海洋大学校园网账号是什么？</t>
+          <t>新生线上报到一般通过什么系统完成？</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>报到与迎新</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>账号</t>
+          <t>线上报到</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>3.98</v>
+        <v>6.44</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -1124,35 +1174,43 @@
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>校园网有问题去哪里看或找谁？</t>
+          <t>不同校区的图书馆分别在哪里？</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>校区识别与地点</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>图书馆分布</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>4.21</v>
+        <v>21.02</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -1173,15 +1231,19 @@
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>22</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>大连海洋大学心理咨询怎么网站预约？</t>
+          <t>不同校区的心理咨询服务怎么区分？</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1191,7 +1253,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>网站预约</t>
+          <t>校区服务</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1199,9 +1261,13 @@
           <t>是</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>7.21</v>
+        <v>24.44</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -1222,39 +1288,47 @@
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>大连海洋大学校园网账号是什么？</t>
+          <t>如果我不知道自己属于哪个校区，应该先看什么信息？</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>校区识别与地点</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>账号</t>
+          <t>校区确认</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>3.18</v>
+        <v>21.58</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1347,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1303,7 +1377,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="L16" t="n">
@@ -1330,7 +1404,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1387,7 +1461,7 @@
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1417,7 +1491,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="L18" t="n">
@@ -1444,7 +1518,7 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1474,7 +1548,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="L19" t="n">
@@ -1550,7 +1624,7 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1580,7 +1654,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -1607,7 +1681,7 @@
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1637,7 +1711,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="L22" t="n">
@@ -1664,7 +1738,7 @@
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1694,7 +1768,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="L23" t="n">
@@ -1770,7 +1844,7 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1800,7 +1874,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="L25" t="n">
@@ -1923,39 +1997,47 @@
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>大连海洋大学校园网账号是什么？</t>
+          <t>新生入学后什么时候完成学籍注册？</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>教务与学籍</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>账号</t>
+          <t>新生学籍注册</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L28" t="n">
-        <v>3.82</v>
+        <v>21.94</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -1972,35 +2054,43 @@
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>校园网有问题去哪里看或找谁？</t>
+          <t>学籍注册后在哪里核验自己的学籍信息？</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>教务与学籍</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>学籍核验</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L29" t="n">
-        <v>2.63</v>
+        <v>20.24</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -2021,35 +2111,43 @@
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>校园网有问题去哪里看或找谁？</t>
+          <t>教务相关问题应该找哪个部门？</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>教务与学籍</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>部门分工</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L30" t="n">
-        <v>3.86</v>
+        <v>20.36</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -2070,35 +2168,43 @@
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>校园网有问题去哪里看或找谁？</t>
+          <t>选课问题一般归哪个科室或部门管理？</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>教务与学籍</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>选课</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L31" t="n">
-        <v>3.2</v>
+        <v>22.03</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -2119,35 +2225,43 @@
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>26</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>校园网有问题去哪里看或找谁？</t>
+          <t>成绩查询或成绩相关问题应该找哪里？</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>教务与学籍</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>咨询</t>
+          <t>成绩</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L32" t="n">
-        <v>3.84</v>
+        <v>22.3</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -2168,35 +2282,43 @@
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>大连海洋大学心理咨询怎么电话预约？</t>
+          <t>学籍异动、注册、证明办理一般归谁负责？</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>教务与学籍</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>电话预约</t>
+          <t>学籍/证明</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L33" t="n">
-        <v>2.17</v>
+        <v>29.71</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -2217,35 +2339,43 @@
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>28</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>学生校园网账号是不是学号？</t>
+          <t>新生入学后第一周最应该熟悉哪些教务事项？</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>教务与学籍</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>账号</t>
+          <t>第一周事项</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L34" t="n">
-        <v>1.64</v>
+        <v>21.23</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -2266,35 +2396,43 @@
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>大连海洋大学校园网账号是什么？</t>
+          <t>学年注册一般在什么时候完成？</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>教务与学籍</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>账号</t>
+          <t>学年注册</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L35" t="n">
-        <v>4.13</v>
+        <v>23.72</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -2315,35 +2453,43 @@
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>大连海洋大学心理咨询怎么网站预约？</t>
+          <t>大连海洋大学图书馆有哪些主要服务？</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>图书馆</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>网站预约</t>
+          <t>服务总览</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L36" t="n">
-        <v>3.38</v>
+        <v>22.7</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -2364,35 +2510,43 @@
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>大连海洋大学心理咨询怎么网站预约？</t>
+          <t>图书馆可以预约座位吗？</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>心理健康</t>
+          <t>图书馆</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>网站预约</t>
+          <t>座位预约</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L37" t="n">
-        <v>3.61</v>
+        <v>33.73</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -2413,35 +2567,43 @@
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>大连海洋大学校园网账号是什么？</t>
+          <t>新生第一次进图书馆要注意什么？</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>图书馆</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>账号</t>
+          <t>入馆规定</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L38" t="n">
-        <v>3.23</v>
+        <v>23.8</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -2462,25 +2624,29 @@
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>35</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>校园网账号开通和使用规则是什么？</t>
+          <t>图书借阅规则在哪里看？</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>图书馆</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>规则</t>
+          <t>借阅规定</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2488,9 +2654,13 @@
           <t>是</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L39" t="n">
-        <v>5.41</v>
+        <v>23.1</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -2511,35 +2681,43 @@
       </c>
       <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>36</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>校园卡绑定后可以做什么？</t>
+          <t>校园一卡通能不能用于图书馆？</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>校园卡</t>
+          <t>图书馆</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>使用</t>
+          <t>一卡通</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L40" t="n">
-        <v>4.77</v>
+        <v>26.97</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -2560,35 +2738,43 @@
       </c>
       <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>37</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>校园卡丢了怎么办？</t>
+          <t>不同校区图书馆资源怎么找？</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>校园卡</t>
+          <t>图书馆</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>挂失/解挂</t>
+          <t>校区资源</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L41" t="n">
-        <v>4.94</v>
+        <v>26.22</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -2611,7 +2797,7 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2641,7 +2827,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="L42" t="n">
@@ -2668,7 +2854,7 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2725,7 +2911,7 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2782,7 +2968,7 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2812,7 +2998,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="L45" t="n">
@@ -2837,15 +3023,19 @@
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>43</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>大连海洋大学心理咨询怎么电话预约？</t>
+          <t>新生刚入学适应困难时，可以找学校哪些心理支持资源？</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2855,17 +3045,21 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>电话预约</t>
+          <t>适应支持</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L46" t="n">
-        <v>3.07</v>
+        <v>22.89</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -2886,39 +3080,47 @@
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>38</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>校园卡丢了怎么办？</t>
+          <t>家庭经济困难学生认定怎么申请？</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>校园卡</t>
+          <t>资助与帮扶</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>挂失/解挂</t>
+          <t>困难认定</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L47" t="n">
-        <v>3.65</v>
+        <v>28.62</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2935,25 +3137,29 @@
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>39</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>大连海洋大学校园网账号是什么？</t>
+          <t>国家助学金的基本申请条件是什么？</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>资助与帮扶</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>账号</t>
+          <t>国家助学金</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -2961,13 +3167,17 @@
           <t>是</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L48" t="n">
-        <v>5.18</v>
+        <v>24.74</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2984,39 +3194,47 @@
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>40</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>学生校园网账号是不是学号？</t>
+          <t>国家助学金分几个等级？</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>资助与帮扶</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>账号</t>
+          <t>国家助学金</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L49" t="n">
-        <v>1.8</v>
+        <v>25.01</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3033,39 +3251,47 @@
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>学生校园网账号是不是学号？</t>
+          <t>退役士兵学生是否享受国家助学金？</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>校园网</t>
+          <t>资助与帮扶</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>账号</t>
+          <t>国家助学金</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L50" t="n">
-        <v>2.71</v>
+        <v>24.47</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -3082,39 +3308,47 @@
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>校园卡丢了怎么办？</t>
+          <t>入学报到时如果暂时交不起费用怎么办？</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>校园卡</t>
+          <t>资助与帮扶</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>挂失/解挂</t>
+          <t>暂缓缴费/绿色通道</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>否</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
       <c r="L51" t="n">
-        <v>4.3</v>
+        <v>20.91</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
